--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-022_申請提出_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-022_申請提出_オンライン詳細設計書.xlsx
@@ -333,7 +333,7 @@
       <row>16</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8572500" cy="14458950"/>
+    <ext cx="8572500" cy="14868525"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜022)の概要。本書はそのうち ONL-022 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-022 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>status=PENDING、current_step=1、submitted_at=now(JST)、days=3.0。deleteByRequestId が 1 回、startApproval が 1 回</t>
+          <t>status=PENDING、current_step=1、submitted_at=now(clock)、days=3.0。deleteByRequestId が 1 回、startApproval が 1 回</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -2391,7 +2391,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2450,6 +2450,30 @@
         </is>
       </c>
       <c r="E2" s="7" t="inlineStr"/>
+    </row>
+    <row r="3" ht="64" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/03</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>・実装に合わせて逆反映：Controller は Authentication#getName() でユーザーIDを取得、日時は Clock Bean（Asia/Tokyo）注入（コードを正とする）
+・leaveTypeId が null の再検証は NPE ではなく E-002 を返す</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4258,7 +4282,7 @@
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>public SubmitRequestResponse submit(@AuthenticationPrincipal Jwt jwt, @PathVariable Long id)</t>
+          <t>public SubmitRequestResponse submit(Authentication auth, @PathVariable Long id)</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -4321,17 +4345,17 @@
     <row r="8" ht="19" customHeight="1">
       <c r="A8" s="7" t="inlineStr">
         <is>
-          <t>jwt</t>
+          <t>auth</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Jwt</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>認証済みトークン（sub = users.id）</t>
+          <t>認証情報（Spring Security が注入）。getName() = users.id（JWT の sub）</t>
         </is>
       </c>
       <c r="D8" s="9" t="n"/>
@@ -4399,7 +4423,7 @@
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>1. Long userId = Long.valueOf(jwt.getSubject());
+          <t>1. Long userId = Long.valueOf(auth.getName());
 2. return requestService.submit(id, userId);
 リクエストボディは受け取らない（@RequestBody を付けない）。本文が送られても無視する。
 クラスコメントに処理ID（ONL-022）を記載する（KF-DD-006 規約）。</t>
@@ -4621,8 +4645,8 @@
       </c>
       <c r="B26" s="12" t="inlineStr">
         <is>
-          <t>today = LocalDate.now(JST);
-now   = LocalDateTime.now(JST).truncatedTo(ChronoUnit.SECONDS);
+          <t>today = LocalDate.now(clock);
+now   = LocalDateTime.now(clock).truncatedTo(ChronoUnit.SECONDS);
 User user = userRepository.findByIdForUpdate(userId)                  // ② 申請者を行ロック（ONL-005 と同じ順序）
         .filter(u -&gt; "ACTIVE".equals(u.getStatus()))
         .orElseThrow(RequestService::forbidden);                      //    なし／INACTIVE → E-010

--- a/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-022_申請提出_オンライン詳細設計書.xlsx
+++ b/docs/03_詳細設計/01_オンライン設計/KF-DD-ONL-022_申請提出_オンライン詳細設計書.xlsx
@@ -273,7 +273,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10953750" cy="5124450"/>
+    <ext cx="10953750" cy="6029325"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -303,7 +303,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="10953750" cy="12449175"/>
+    <ext cx="10953750" cy="11934825"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -698,7 +698,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>ONL-022 申請提出（機能 F-03 打刻修正申請 / F-04 休暇申請（下書き・差戻しの提出））</t>
+          <t>ONL-022 申請提出（機能 F-03 打刻修正申請（休憩・離席修正申請を含む） / F-04 休暇申請（下書き・差戻しの提出））</t>
         </is>
       </c>
     </row>
@@ -722,7 +722,7 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
     </row>
@@ -765,7 +765,7 @@
     <row r="17">
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜023)の概要。本書はそのうち ONL-022 を実装レベルまで詳細化したもの。
+          <t>本書の位置づけ：KF-DD-001 は全オンライン処理(ONL-001〜026)の概要。本書はそのうち ONL-022 を実装レベルまで詳細化したもの。
 本書の目的：本書だけを見て、この処理のバックエンドを実装・単体テストできる粒度で記述する。</t>
         </is>
       </c>
@@ -835,7 +835,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="79" customHeight="1">
+    <row r="4" ht="94" customHeight="1">
       <c r="A4" s="7" t="inlineStr">
         <is>
           <t>E-002</t>
@@ -848,12 +848,12 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>入力内容が正しくありません。／休暇種別が正しくありません。／この休暇種別では半日単位を指定できません。／指定期間に取得できる営業日がありません。／理由は必須入力です。／修正後の出勤・退勤時刻は必須入力です。</t>
+          <t>入力内容が正しくありません。／休暇種別が正しくありません。／この休暇種別では半日単位を指定できません。／指定期間に取得できる営業日がありません。／理由は必須入力です。／修正後の出勤・退勤時刻は必須入力です。／休憩・離席の種別と開始・終了時刻は必須入力です。</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>id が数値でない、または保存済みの内容が提出条件を満たさない（休暇種別が無効・営業日数 0・打刻修正の理由／時刻の欠落）</t>
+          <t>id が数値でない、または保存済みの内容が提出条件を満たさない（休暇種別が無効・営業日数 0・打刻修正の理由／時刻の欠落・休憩離席修正の理由／種別／時刻の欠落）</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
@@ -862,7 +862,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="109" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>E-003</t>
@@ -875,17 +875,17 @@
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
-          <t>修正後の退勤時刻は出勤時刻より後の時刻を指定してください。</t>
+          <t>修正後の退勤時刻は出勤時刻より後の時刻を指定してください。／対象日に出勤打刻がないため、休憩・離席を修正できません。／終了時刻は開始時刻より後の時刻を指定してください。／休憩・離席の時刻は出勤 HH:mm 以降（退勤済みは 出勤 HH:mm〜退勤 HH:mm）の範囲内で指定してください。</t>
         </is>
       </c>
       <c r="D5" s="7" t="inlineStr">
         <is>
-          <t>打刻修正で退勤時刻 ≦ 出勤時刻</t>
+          <t>打刻修正で退勤時刻 ≦ 出勤時刻／休憩離席修正で対象日に出勤打刻がない・終了≦開始・出勤〜退勤の範囲外</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>RequestService#revalidateForSubmit</t>
+          <t>RequestService#revalidateForSubmit／AttendanceService#checkBreakCorrection</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="64" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>E-005</t>
@@ -929,17 +929,17 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>同一期間に既に申請があります。</t>
+          <t>同一期間に既に申請があります。／他の休憩・離席の時間帯と重なっています。</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>休暇: PENDING / APPROVED と期間重複（AM+PM 同日は除く）／打刻修正: 同日の PENDING あり</t>
+          <t>休暇: PENDING / APPROVED と期間重複（AM+PM 同日は除く）／打刻修正・休憩離席修正: 同じ種別・同日の PENDING あり／休憩離席修正: 対象日の既存の区間と時間帯が重なる</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>RequestService#checkSubmittable（checkOverlap）</t>
+          <t>RequestService#checkSubmittable／AttendanceService#checkBreakCorrection</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>認証情報が無効、または有効期限が切れています。再度ログインしてください。</t>
+          <t>認証が必要です。再度ログインしてください。</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>トークンなし・不正・期限切れ（Controller 到達前）</t>
+          <t>トークンなし・不正・期限切れ・パスワード変更後の旧トークン・無効ユーザー（Controller 到達前）</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>RestAuthenticationEntryPoint（ONL-001）</t>
+          <t>SecurityConfig（AuthenticationEntryPoint / ActiveUserFilter）</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E46"/>
+  <dimension ref="A2:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1824,179 +1824,222 @@
       </c>
       <c r="E20" s="7" t="inlineStr"/>
     </row>
-    <row r="22">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>9.2 RequestService#submit  通知（Mockito でモック）</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-      <c r="E22" s="10" t="n"/>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>No.</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>区分</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>観点・条件</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>期待結果</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="34" customHeight="1">
+    <row r="21" ht="64" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C21" s="7" t="inlineStr">
+        <is>
+          <t>本人の DRAFT（BREAK_CORRECTION・理由あり・BREAK 12:00〜13:00・対象日に出勤 09:00 / 退勤 18:00 の打刻あり）を提出</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>PENDING。validateBreakCorrection が 1 回呼ばれ、leave_type_id・unit・days は null のまま。通知の文面は「休憩・離席修正申請（対象日 …）」</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>corrected_break_* は変更されない</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION の DRAFT で理由が空白</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>E-002「理由は必須入力です。」</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>理由の確認が先</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION の DRAFT で種別／開始／終了のいずれかが null</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>E-002「休憩・離席の種別と開始・終了時刻は必須入力です。」</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>validateBreakCorrection は呼ばれない</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="49" customHeight="1">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>正常</t>
+          <t>異常</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>本人の DRAFT を提出（上長あり）</t>
+          <t>BREAK_CORRECTION の提出時、対象日に打刻行がない／clock_in が NULL（下書き後に打刻が修正された場合を含む）</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>notify(上長ID, REQUEST_SUBMITTED, 本文, 申請ID) が 1 回</t>
+          <t>E-003「対象日に出勤打刻がないため、休憩・離席を修正できません。」/ 400</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>本文に申請者名・種別・期間を含み理由は含まない</t>
+          <t>status は変わらない・旧ステップは削除されない</t>
         </is>
       </c>
     </row>
     <row r="25" ht="34" customHeight="1">
       <c r="A25" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION の提出時、範囲外（出勤 09:00 より前の開始／退勤 18:00 より後の終了）</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>E-003「休憩・離席の時刻は出勤 09:00〜退勤 18:00の範囲内で指定してください。」</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26" ht="49" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION の提出時、既存の区間と時間帯が重なる（下書き作成後に ONL-024/025 で打刻された場合を含む）</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>E-005「他の休憩・離席の時間帯と重なっています。」/ 409</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>隣接は成功。同種別の継続中の区間は重なり判定から除外</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="64" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
+        <is>
+          <t>BREAK_CORRECTION で同じ対象日の BREAK_CORRECTION が PENDING</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>E-005「同一期間に既に申請があります。」/ 409</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>休憩/離席の種別違いでも E-005（自分自身は DRAFT / RETURNED のため対象外）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="49" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
-        <is>
-          <t>上長なし・有効な ADMIN が 2 名</t>
-        </is>
-      </c>
-      <c r="D25" s="7" t="inlineStr">
-        <is>
-          <t>notify が管理者 2 名に各 1 回（requestId 同一）</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>申請者が ADMIN の場合は本人を除く</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>境界</t>
-        </is>
-      </c>
-      <c r="C26" s="7" t="inlineStr">
-        <is>
-          <t>通知先が 0 件</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr">
-        <is>
-          <t>提出は成功（PENDING）、notify は呼ばれない</t>
-        </is>
-      </c>
-      <c r="E26" s="7" t="inlineStr">
-        <is>
-          <t>エラーにしない</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>notify が例外（IllegalArgumentException）</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>例外が伝播（E-012）</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>結合テストでロールバックを確認（#27）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="34" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>異常</t>
-        </is>
-      </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>E-010 / E-015 / E-016 / E-002 / E-004 / E-005 の場合</t>
+          <t>差戻し（RETURNED）の BREAK_CORRECTION を再提出</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>notify は呼ばれない</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr"/>
+          <t>PENDING。旧ステップ削除 → 新ステップ作成の順。再度 validateBreakCorrection が実行される</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>再提出時にも打刻照合</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>9.3 RequestController（MockMvc / API テスト）</t>
+          <t>9.2 RequestService#submit  通知（Mockito でモック）</t>
         </is>
       </c>
       <c r="B30" s="9" t="n"/>
@@ -2034,7 +2077,7 @@
     <row r="32" ht="34" customHeight="1">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
@@ -2044,70 +2087,78 @@
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>本人の DRAFT に POST /api/requests/15/submit</t>
+          <t>本人の DRAFT を提出（上長あり）</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>200、body に requestId=15 と status=PENDING</t>
+          <t>notify(上長ID, REQUEST_SUBMITTED, 本文, 申請ID) が 1 回</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>JWT の sub のユーザーで処理される</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="19" customHeight="1">
+          <t>本文に申請者名・種別・期間を含み理由は含まない</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
       <c r="A33" s="7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>正常</t>
         </is>
       </c>
       <c r="C33" s="7" t="inlineStr">
         <is>
-          <t>POST /api/requests/abc/submit</t>
+          <t>上長なし・有効な ADMIN が 2 名</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>400 E-002（500 にならない）</t>
-        </is>
-      </c>
-      <c r="E33" s="7" t="inlineStr"/>
-    </row>
-    <row r="34" ht="19" customHeight="1">
+          <t>notify が管理者 2 名に各 1 回（requestId 同一）</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>申請者が ADMIN の場合は本人を除く</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="34" customHeight="1">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>異常</t>
+          <t>境界</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>提出不可の状態／他人の申請／存在しない ID</t>
+          <t>通知先が 0 件</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>409 E-016／403 E-010／404 E-015</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr"/>
+          <t>提出は成功（PENDING）、notify は呼ばれない</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>エラーにしない</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="34" customHeight="1">
       <c r="A35" s="7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B35" s="7" t="inlineStr">
@@ -2117,268 +2168,429 @@
       </c>
       <c r="C35" s="7" t="inlineStr">
         <is>
+          <t>notify が例外（IllegalArgumentException）</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>例外が伝播（E-012）</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>結合テストでロールバックを確認（#27）</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="34" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
+        <is>
+          <t>E-010 / E-015 / E-016 / E-002 / E-004 / E-005 の場合</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>notify は呼ばれない</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>9.3 RequestController（MockMvc / API テスト）</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n"/>
+      <c r="C38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="10" t="n"/>
+    </row>
+    <row r="39" ht="19" customHeight="1">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>No.</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>区分</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>観点・条件</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>期待結果</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="34" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>本人の DRAFT に POST /api/requests/15/submit</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>200、body に requestId=15 と status=PENDING</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>JWT の sub のユーザーで処理される</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="19" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>POST /api/requests/abc/submit</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>400 E-002（500 にならない）</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>提出不可の状態／他人の申請／存在しない ID</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>409 E-016／403 E-010／404 E-015</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43" ht="34" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>異常</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
           <t>Authorization なし</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>401、{code:"E-001", …} の JSON（AuthenticationEntryPoint）</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
         <is>
           <t>9.4 結合テスト（実 DB / Testcontainers）</t>
         </is>
       </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="10" t="n"/>
-    </row>
-    <row r="38" ht="19" customHeight="1">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="B45" s="9" t="n"/>
+      <c r="C45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="10" t="n"/>
+    </row>
+    <row r="46" ht="19" customHeight="1">
+      <c r="A46" s="6" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>区分</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>観点・条件</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D46" s="6" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="49" customHeight="1">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
+    <row r="47" ht="49" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>異常</t>
         </is>
       </c>
-      <c r="C39" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>通知の登録で例外を起こす（モックの NotificationService）</t>
         </is>
       </c>
-      <c r="D39" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>トランザクション全体がロールバック。status は RETURNED のまま、旧 approval_steps も残る</t>
         </is>
       </c>
-      <c r="E39" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>削除のロールバック確認</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="49" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
+    <row r="48" ht="49" customHeight="1">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>DRAFT を提出後、requests と approval_steps を確認</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>status=PENDING、approval_steps に WAITING が 1〜2 行。ONL-009 の承認待ち一覧に表示される</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr"/>
-    </row>
-    <row r="41" ht="64" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49" ht="64" customHeight="1">
+      <c r="A49" s="7" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>RETURNED（1 段目承認済み→差戻し）を再提出後、approval_steps を確認</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>旧ステップ（APPROVED/RETURNED・コメントあり）は削除され、WAITING の新ステップのみ。UNIQUE(request_id, step_no) 違反なし</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>Hibernate の INSERT/DELETE 順序問題がないことの確認</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="49" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="inlineStr">
+    <row r="50" ht="49" customHeight="1">
+      <c r="A50" s="7" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>境界</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>同じ申請に POST を 2 スレッドで同時実行</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>1 つだけ成功（200）、もう 1 つは E-016（409）。notifications は承認者ごとに 1 行</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>行ロックの確認</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="49" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="inlineStr">
+    <row r="51" ht="49" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>境界</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>提出（ONL-022）と取下げ（ONL-008）／承認（ONL-010）の同時実行</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>どちらか一方のみ成功。提出が先なら取下げは PENDING として成功、取下げが先なら提出は E-016</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>デッドロックしない</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="49" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="inlineStr">
+    <row r="52" ht="49" customHeight="1">
+      <c r="A52" s="7" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>提出後に notifications を確認</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>type=REQUEST_SUBMITTED、request_id=申請ID、is_read=FALSE の行が承認者ごとに 1 行</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>fk_notifications_request_id を満たす</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="34" customHeight="1">
-      <c r="A45" s="7" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="inlineStr">
+    <row r="53" ht="34" customHeight="1">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C45" s="7" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>提出後に requests.updated_at を確認</t>
         </is>
       </c>
-      <c r="D45" s="7" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>提出前より新しい（トリガで更新）</t>
         </is>
       </c>
-      <c r="E45" s="7" t="inlineStr">
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>アプリは updated_at を設定しない</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="34" customHeight="1">
-      <c r="A46" s="7" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
+    <row r="54" ht="34" customHeight="1">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>正常</t>
         </is>
       </c>
-      <c r="C46" s="7" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>提出後に ONL-006 / ONL-007 で取得</t>
         </is>
       </c>
-      <c r="D46" s="7" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>status=PENDING、submittedAt が更新され、steps[].current が現在段で true</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr"/>
+      <c r="E54" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A37:E37"/>
+    <mergeCell ref="A45:E45"/>
     <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A38:E38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2391,7 +2603,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2474,6 +2686,29 @@
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr"/>
+    </row>
+    <row r="4" ht="124" customHeight="1">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>2026/10/05</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>Wang Sheng</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正申請（BREAK_CORRECTION）の再提出に対応：revalidateForSubmit に BREAK_CORRECTION を追加（理由必須、種別・開始・終了の揃い、AttendanceService#validateBreakCorrection による対象日の打刻照合 → E-003 / E-005）、同日重複（E-005）を申請種別単位に更新、通知文面・使用テーブル（attendance_records / attendance_breaks: R）・マッピング・SQL・エラー・テスト観点を更新。SUBMITTABLE は RequestStatus ではなく RequestService 内の private 定数である実装に合わせて記述を修正。401 のメッセージを実装に合わせて修正</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2487,7 +2722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F43"/>
+  <dimension ref="A2:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2534,7 +2769,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>F-03 打刻修正申請 / F-04 休暇申請（下書き・差戻しの提出）</t>
+          <t>F-03 打刻修正申請（休憩・離席修正申請を含む） / F-04 休暇申請（下書き・差戻しの提出）</t>
         </is>
       </c>
       <c r="C4" s="9" t="n"/>
@@ -2574,7 +2809,7 @@
       <c r="E6" s="9" t="n"/>
       <c r="F6" s="10" t="n"/>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="49" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
           <t>目的</t>
@@ -2582,7 +2817,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>下書き（DRAFT）または差戻し（RETURNED）の自分の申請を、承認待ち（PENDING）として提出（再提出）する。ONL-005 の提出時と同じ検証（残日数 E-004・期間重複 E-005）と承認ルート作成・承認者への通知を行う。</t>
+          <t>下書き（DRAFT）または差戻し（RETURNED）の自分の申請（休暇・打刻修正・休憩離席修正）を、承認待ち（PENDING）として提出（再提出）する。ONL-005 の提出時と同じ検証（残日数 E-004・期間重複／同日重複 E-005）に加え、休憩・離席修正申請は対象日の打刻との照合（E-003 / E-005）を行い、承認ルート作成・承認者への通知を行う。</t>
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
@@ -2622,7 +2857,7 @@
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10" ht="49" customHeight="1">
+    <row r="10" ht="64" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
         <is>
           <t>事後条件</t>
@@ -2630,7 +2865,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>requests.status = PENDING、current_step = 1（上長なしは 2）、submitted_at = 現在日時（再提出時は上書き）、休暇は days を営業日数で再計算して更新（updated_at は DB トリガで自動更新）。旧 approval_steps を全て削除し、承認ルートを作り直して 1〜2 行登録する。現在の承認者へ画面内通知（type=REQUEST_SUBMITTED、requestId=申請ID）を登録する。休暇残日数（leave_balances）は更新しない（消化は承認時 ONL-010）。</t>
+          <t>requests.status = PENDING、current_step = 1（上長なしは 2）、submitted_at = 現在日時（再提出時は上書き）、休暇は days を営業日数で再計算して更新（updated_at は DB トリガで自動更新）。旧 approval_steps を全て削除し、承認ルートを作り直して 1〜2 行登録する。現在の承認者へ画面内通知（type=REQUEST_SUBMITTED、requestId=申請ID）を登録する。休暇残日数（leave_balances）は更新しない（消化は承認時 ONL-010）。休憩・離席修正申請は corrected_break_* を変更せず、提出時点の打刻との照合だけを行う（反映は最終承認 ONL-010）。</t>
         </is>
       </c>
       <c r="C10" s="9" t="n"/>
@@ -2638,7 +2873,7 @@
       <c r="E10" s="9" t="n"/>
       <c r="F10" s="10" t="n"/>
     </row>
-    <row r="11" ht="19" customHeight="1">
+    <row r="11" ht="34" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
           <t>使用テーブル</t>
@@ -2646,7 +2881,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>requests: R/U, approval_steps: C/D, users: R, leave_types: R, leave_balances: R, holidays: R, notifications: C（NotificationService 経由）</t>
+          <t>requests: R/U, approval_steps: C/D, users: R, leave_types: R, leave_balances: R, holidays: R, notifications: C（NotificationService 経由）, attendance_records: R・attendance_breaks: R（休憩・離席修正申請のみ）</t>
         </is>
       </c>
       <c r="C11" s="9" t="n"/>
@@ -2922,7 +3157,7 @@
       <c r="E26" s="9" t="n"/>
       <c r="F26" s="10" t="n"/>
     </row>
-    <row r="27" ht="49" customHeight="1">
+    <row r="27" ht="64" customHeight="1">
       <c r="A27" s="7" t="inlineStr">
         <is>
           <t>ONL-005</t>
@@ -2935,7 +3170,7 @@
       </c>
       <c r="C27" s="7" t="inlineStr">
         <is>
-          <t>RequestService#checkSubmittable / startApproval / calcDays / buildSubmittedMessage / forbidden / badInput、ApprovalRouteService、NotificationService#notify（4引数・定義元）、RequestRepository#findByIdForUpdate、UserRepository#findByIdForUpdate の定義</t>
+          <t>RequestService#checkSubmittable / startApproval / calcDays / buildSubmittedMessage / forbidden / badInput、ApprovalRouteService、NotificationService#notify（4引数・定義元）、RequestRepository#findByIdForUpdate、UserRepository#findByIdForUpdate の定義、AttendanceService#validateBreakCorrection / checkBreakCorrection（休憩・離席修正の検証）の定義</t>
         </is>
       </c>
       <c r="D27" s="9" t="n"/>
@@ -2982,170 +3217,158 @@
       <c r="E29" s="9" t="n"/>
       <c r="F29" s="10" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+    <row r="30" ht="19" customHeight="1">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>ONL-010</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>承認</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>最終承認時に AttendanceService#applyBreakCorrection（同じ checkBreakCorrection を再実施）で区間を反映</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="10" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>1.3 対象クラス一覧（パッケージ：com.example.kintaiflow）</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n"/>
-      <c r="C31" s="9" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="9" t="n"/>
-      <c r="F31" s="10" t="n"/>
-    </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="B32" s="9" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="10" t="n"/>
+    </row>
+    <row r="33" ht="19" customHeight="1">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>パッケージ</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>クラス名</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>責務</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>ファイル</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>新規/既存</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="34" customHeight="1">
-      <c r="A33" s="7" t="inlineStr">
+    <row r="34" ht="34" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>controller</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>RequestController</t>
         </is>
       </c>
-      <c r="C33" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>Controller</t>
         </is>
       </c>
-      <c r="D33" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>本処理は submit を追加</t>
         </is>
       </c>
-      <c r="E33" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>controller/RequestController.java</t>
         </is>
       </c>
-      <c r="F33" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-005 で定義）。submit を追加</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="94" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="35" ht="109" customHeight="1">
+      <c r="A35" s="7" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>RequestService</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
-        <is>
-          <t>本処理は submit / revalidateForSubmit / notFound / notSubmittable を追加。checkSubmittable / startApproval / calcDays は ONL-005 のものを共用</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>本処理は submit / revalidateForSubmit / notFound / notSubmittable を追加（SUBMITTABLE は private 定数）。checkSubmittable / startApproval / calcDays は ONL-005 のものを共用</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>service/RequestService.java</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-005 で定義）。submit ほかを追加</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="49" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="36" ht="49" customHeight="1">
+      <c r="A36" s="7" t="inlineStr">
         <is>
           <t>service</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>ApprovalRouteService</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>Service</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>承認ルート作成 createSteps / 通知先決定 resolveCurrentApproverIds を使用</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>service/ApprovalRouteService.java</t>
-        </is>
-      </c>
-      <c r="F35" s="7" t="inlineStr">
-        <is>
-          <t>既存（ONL-005 で定義）</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="34" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>service</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>NotificationService</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>Service</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>承認者への通知 notify(userId, type, message, requestId)</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>service/NotificationService.java</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -3157,27 +3380,27 @@
     <row r="37" ht="34" customHeight="1">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>repository</t>
+          <t>service</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>RequestRepository</t>
+          <t>NotificationService</t>
         </is>
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>行ロック付き取得 findByIdForUpdate を使用、save で更新</t>
+          <t>承認者への通知 notify(userId, type, message, requestId)</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>repository/RequestRepository.java</t>
+          <t>service/NotificationService.java</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -3186,35 +3409,35 @@
         </is>
       </c>
     </row>
-    <row r="38" ht="34" customHeight="1">
+    <row r="38" ht="64" customHeight="1">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>repository</t>
+          <t>service</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>UserRepository</t>
+          <t>AttendanceService</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Repository</t>
+          <t>Service</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>申請者の行ロック付き取得 findByIdForUpdate を使用</t>
+          <t>休憩・離席修正申請の検証 validateBreakCorrection（再提出時の revalidateForSubmit から呼ぶ）</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>repository/UserRepository.java</t>
+          <t>service/AttendanceService.java</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>既存（ONL-005 で定義）</t>
+          <t>既存（ONL-002 / ONL-005 で定義）</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3449,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>ApprovalStepRepository</t>
+          <t>RequestRepository</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
@@ -3236,44 +3459,44 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>旧ステップの一括削除 deleteByRequestId を追加</t>
+          <t>行ロック付き取得 findByIdForUpdate を使用、save で更新</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>repository/ApprovalStepRepository.java</t>
+          <t>repository/RequestRepository.java</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>既存（ONL-005 で定義）。deleteByRequestId を追加</t>
+          <t>既存（ONL-005 で定義）</t>
         </is>
       </c>
     </row>
     <row r="40" ht="34" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>entity</t>
+          <t>repository</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Request / ApprovalStep</t>
+          <t>UserRepository</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Entity</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>requests / approval_steps のマッピング</t>
+          <t>申請者の行ロック付き取得 findByIdForUpdate を使用</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>entity/Request.java ほか</t>
+          <t>repository/UserRepository.java</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -3285,101 +3508,165 @@
     <row r="41" ht="34" customHeight="1">
       <c r="A41" s="7" t="inlineStr">
         <is>
-          <t>entity</t>
+          <t>repository</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>RequestStatus</t>
+          <t>ApprovalStepRepository</t>
         </is>
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>定数クラス</t>
+          <t>Repository</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>SUBMITTABLE（DRAFT, RETURNED）を追加</t>
+          <t>旧ステップの一括削除 deleteByRequestId を追加</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>entity/RequestStatus.java</t>
+          <t>repository/ApprovalStepRepository.java</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>既存（ONL-005 で定義）。SUBMITTABLE を追加</t>
+          <t>既存（ONL-005 で定義）。deleteByRequestId を追加</t>
         </is>
       </c>
     </row>
     <row r="42" ht="34" customHeight="1">
       <c r="A42" s="7" t="inlineStr">
         <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Request / ApprovalStep</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>requests / approval_steps のマッピング</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>entity/Request.java ほか</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-005 で定義）</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>RequestStatus</t>
+        </is>
+      </c>
+      <c r="C43" s="7" t="inlineStr">
+        <is>
+          <t>定数クラス</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>DRAFT / RETURNED などの状態定数（変更なし。提出可能な状態の集合 SUBMITTABLE は RequestService 内の private 定数）</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>entity/RequestStatus.java</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>既存（ONL-005 で定義）。本処理での変更なし</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="34" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
           <t>dto</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>SubmitRequestResponse</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>DTO(record)</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>正常応答 {requestId, status}</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>dto/SubmitRequestResponse.java</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>新規</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="49" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="45" ht="49" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>exception</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>BusinessException / GlobalExceptionHandler / ErrorResponse</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>共通部品</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>業務エラー・共通エラー応答（handleTypeMismatch は ONL-001 で定義）</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>exception/・dto/</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>既存（ONL-001）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="28">
+  <mergeCells count="29">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="C17:F17"/>
@@ -3392,6 +3679,8 @@
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="A14:F14"/>
     <mergeCell ref="B11:F11"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="C30:F30"/>
     <mergeCell ref="C15:F15"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="C24:F24"/>
@@ -3399,7 +3688,6 @@
     <mergeCell ref="C20:F20"/>
     <mergeCell ref="C26:F26"/>
     <mergeCell ref="C29:F29"/>
-    <mergeCell ref="A31:F31"/>
     <mergeCell ref="C16:F16"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="B9:F9"/>
@@ -3827,7 +4115,7 @@
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="10" t="n"/>
     </row>
-    <row r="20" ht="289" customHeight="1">
+    <row r="20" ht="364" customHeight="1">
       <c r="A20" s="11" t="inlineStr">
         <is>
           <t>エラー例</t>
@@ -3841,12 +4129,16 @@
 { "code": "E-004", "message": "休暇残日数が不足しています。", "fieldErrors": [] }
 HTTP 409
 { "code": "E-005", "message": "同一期間に既に申請があります。", "fieldErrors": [] }
+HTTP 400（休憩・離席修正：対象日に出勤打刻がない）
+{ "code": "E-003", "message": "対象日に出勤打刻がないため、休憩・離席を修正できません。", "fieldErrors": [] }
+HTTP 409（休憩・離席修正：他の区間と重複）
+{ "code": "E-005", "message": "他の休憩・離席の時間帯と重なっています。", "fieldErrors": [] }
 HTTP 404
 { "code": "E-015", "message": "対象のデータが見つかりません。", "fieldErrors": [] }
 HTTP 403
 { "code": "E-010", "message": "この操作を行う権限がありません。", "fieldErrors": [] }
 HTTP 401（トークンなし・期限切れ・不正。AuthenticationEntryPoint が返す JSON。Controller には到達しない）
-{ "code": "E-001", "message": "認証情報が無効、または有効期限が切れています。再度ログインしてください。", "fieldErrors": [] }</t>
+{ "code": "E-001", "message": "認証が必要です。再度ログインしてください。", "fieldErrors": [] }</t>
         </is>
       </c>
       <c r="C20" s="9" t="n"/>
@@ -4049,7 +4341,7 @@
       <c r="E8" s="9" t="n"/>
       <c r="F8" s="10" t="n"/>
     </row>
-    <row r="9" ht="64" customHeight="1">
+    <row r="9" ht="139" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
         <is>
           <t>⑥</t>
@@ -4063,18 +4355,18 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>RequestService#revalidateForSubmit。LEAVE: 休暇種別が有効・半日可否・営業日数 ≧ 0.5 日（days を再計算して更新）。CLOCK_CORRECTION: 理由が空でない・出勤／退勤時刻が揃い退勤 ＞ 出勤</t>
+          <t>RequestService#revalidateForSubmit。LEAVE: 休暇種別が有効・半日可否・営業日数 ≧ 0.5 日（days を再計算して更新）。CLOCK_CORRECTION: 理由が空でない・出勤／退勤時刻が揃い退勤 ＞ 出勤。BREAK_CORRECTION: 理由が空でない・種別／開始／終了が揃い、AttendanceService#validateBreakCorrection で対象日の打刻と照合（出勤打刻あり・開始＜終了・出勤〜退勤の範囲内・既存区間と重ならない）</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>判定（No → E-002 / E-003 を返却  HTTP 400）</t>
+          <t>判定（No → E-002 / E-003（400）  ／E-005（409）を返却）</t>
         </is>
       </c>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="10" t="n"/>
     </row>
-    <row r="10" ht="79" customHeight="1">
+    <row r="10" ht="94" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>⑦</t>
@@ -4087,7 +4379,7 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>RequestService#checkSubmittable（ONL-005 と共用）。LEAVE: 残日数 − PENDING 引当 ≧ 日数（上限付き種別のみ）と PENDING / APPROVED の期間重複。CLOCK_CORRECTION: 同日の PENDING。自分自身は DRAFT / RETURNED のため判定に影響しない</t>
+          <t>RequestService#checkSubmittable（ONL-005 と共用）。LEAVE: 残日数 − PENDING 引当 ≧ 日数（上限付き種別のみ）と PENDING / APPROVED の期間重複。CLOCK_CORRECTION / BREAK_CORRECTION: 同じ申請種別・同日の PENDING。自分自身は DRAFT / RETURNED のため判定に影響しない</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
@@ -4235,7 +4527,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F93"/>
+  <dimension ref="A2:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4520,7 +4812,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>申請者と申請を行ロック付きで取得し、本人かつ提出可能な状態（DRAFT / RETURNED）であれば、ONL-005 と同じ検証を行って PENDING に更新し、承認ルートを作り直して承認者へ通知する。</t>
+          <t>申請者と申請を行ロック付きで取得し、本人かつ提出可能な状態（DRAFT / RETURNED）であれば、ONL-005 と同じ検証（休憩・離席修正は打刻照合を含む）を行って PENDING に更新し、承認ルートを作り直して承認者へ通知する。</t>
         </is>
       </c>
       <c r="C19" s="9" t="n"/>
@@ -4655,9 +4947,9 @@
 if (!r.getUserId().equals(userId))                                    // ④ 他人の申請 → E-010 / 403
     throw forbidden();
 String fromStatus = r.getStatus();                                    // 更新前の status を退避
-if (!RequestStatus.SUBMITTABLE.contains(fromStatus))                  // ⑤ DRAFT / RETURNED 以外 → E-016 / 409
+if (!SUBMITTABLE.contains(fromStatus))                  // ⑤ DRAFT / RETURNED 以外 → E-016 / 409
     throw notSubmittable();
-LeaveType leaveType = revalidateForSubmit(r);                         // ⑥ 再検証（LEAVE は days も再計算して r に設定。打刻修正は null）
+LeaveType leaveType = revalidateForSubmit(r);                         // ⑥ 再検証（LEAVE は days も再計算して r に設定。打刻修正・休憩離席修正は null）
 checkSubmittable(userId, r.getRequestType(), leaveType, r.getDays(),
         r.getStartDate(), r.getEndDate(), r.getUnit(), today);          // ⑦ E-004 / E-005（ONL-005 と共用）
 r.setStatus(RequestStatus.PENDING);                                   // ⑧
@@ -4755,7 +5047,7 @@
       <c r="E32" s="9" t="n"/>
       <c r="F32" s="10" t="n"/>
     </row>
-    <row r="33" ht="34" customHeight="1">
+    <row r="33" ht="49" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
           <t>説明</t>
@@ -4763,7 +5055,7 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>下書き・差戻しの申請内容を、提出時の条件で再検証する。LEAVE は休暇種別・半日可否・営業日数を確認し、days を再計算して r に設定する。CLOCK_CORRECTION は理由と時刻の整合を確認する。</t>
+          <t>下書き・差戻しの申請内容を、提出時の条件で再検証する。LEAVE は休暇種別・半日可否・営業日数を確認し、days を再計算して r に設定する。CLOCK_CORRECTION は理由と時刻の整合を、BREAK_CORRECTION は理由・種別・時刻の揃いと対象日の打刻との整合（validateBreakCorrection）を確認する。</t>
         </is>
       </c>
       <c r="C33" s="9" t="n"/>
@@ -4835,7 +5127,7 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>LeaveType（LEAVE）／null（CLOCK_CORRECTION）</t>
+          <t>LeaveType（LEAVE）／null（CLOCK_CORRECTION / BREAK_CORRECTION）</t>
         </is>
       </c>
       <c r="C37" s="9" t="n"/>
@@ -4851,7 +5143,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>BusinessException E-002（400）、E-003（400）</t>
+          <t>BusinessException E-002（400）、E-003（400）、E-005（409）</t>
         </is>
       </c>
       <c r="C38" s="9" t="n"/>
@@ -4859,7 +5151,7 @@
       <c r="E38" s="9" t="n"/>
       <c r="F38" s="10" t="n"/>
     </row>
-    <row r="39" ht="289" customHeight="1">
+    <row r="39" ht="424" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
           <t>処理詳細</t>
@@ -4868,10 +5160,11 @@
       <c r="B39" s="12" t="inlineStr">
         <is>
           <t>if (RequestType.LEAVE.equals(r.getRequestType())) {
-  LeaveType type = leaveTypeRepository.findById(r.getLeaveTypeId())
-      .filter(LeaveType::getIsActive)
+  LeaveType type = (r.getLeaveTypeId() == null ? Optional.&lt;LeaveType&gt;empty()
+          : leaveTypeRepository.findById(r.getLeaveTypeId()))
+      .filter(t -&gt; Boolean.TRUE.equals(t.getIsActive()))
       .orElseThrow(() -&gt; badInput("休暇種別が正しくありません。"));
-  if (!LeaveUnit.FULL.equals(r.getUnit()) &amp;&amp; !type.getAllowHalfDay())
+  if (!LeaveUnit.FULL.equals(r.getUnit()) &amp;&amp; !Boolean.TRUE.equals(type.getAllowHalfDay()))
       throw badInput("この休暇種別では半日単位を指定できません。");
   BigDecimal days = calcDays(r.getStartDate(), r.getEndDate(), r.getUnit());   // 祝日マスタの変更を反映
   if (days.signum() == 0)
@@ -4879,8 +5172,16 @@
   r.setDays(days);
   return type;
 }
-if (r.getReason() == null || r.getReason().isBlank())
-    throw badInput("理由は必須入力です。");                        // 打刻修正は提出時に理由が必須
+if (r.getReason() == null || r.getReason().isBlank())               // 打刻修正・休憩離席修正は提出時に理由が必須
+    throw badInput("理由は必須入力です。");
+if (RequestType.BREAK_CORRECTION.equals(r.getRequestType())) {
+  if (r.getCorrectedBreakKind() == null || r.getCorrectedBreakStart() == null || r.getCorrectedBreakEnd() == null)
+      throw badInput("休憩・離席の種別と開始・終了時刻は必須入力です。");
+  attendanceService.validateBreakCorrection(r.getUserId(), r.getStartDate(),
+      r.getCorrectedBreakKind(), r.getCorrectedBreakStart(), r.getCorrectedBreakEnd());   // E-003 / E-005
+  return null;
+}
+// CLOCK_CORRECTION
 if (r.getCorrectedClockIn() == null || r.getCorrectedClockOut() == null)
     throw badInput("修正後の出勤・退勤時刻は必須入力です。");
 if (!r.getCorrectedClockOut().isAfter(r.getCorrectedClockIn()))
@@ -4901,7 +5202,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>LeaveTypeRepository#findById / calcDays / badInput / BusinessException コンストラクタ</t>
+          <t>LeaveTypeRepository#findById / calcDays / AttendanceService#validateBreakCorrection / badInput / BusinessException コンストラクタ</t>
         </is>
       </c>
       <c r="C40" s="9" t="n"/>
@@ -4909,7 +5210,7 @@
       <c r="E40" s="9" t="n"/>
       <c r="F40" s="10" t="n"/>
     </row>
-    <row r="41" ht="64" customHeight="1">
+    <row r="41" ht="124" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -4918,7 +5219,9 @@
       <c r="B41" s="7" t="inlineStr">
         <is>
           <t>下書きは入力が不完全でも保存できる（ONL-005 の validateInput は draft=true で一部を免除）ため、提出時に ONL-005 の提出時検証と同等の条件を再確認する。日付の前後関係（開始日 ≦ 終了日、対象日 ≦ 本日）は保存時に E-003 で検証済みのため再確認しない。
-営業日数は祝日マスタ（holidays）が保存後に変更されている可能性があるため再計算する。RETURNED の申請は ONL-005 で提出済みのため通常は変化しない。</t>
+営業日数は祝日マスタ（holidays）が保存後に変更されている可能性があるため再計算する。RETURNED の申請は ONL-005 で提出済みのため通常は変化しない。
+休憩・離席修正は、保存時（ONL-005）は形式・整合のみ検証し、打刻との照合は提出時（本処理）に行う。下書きを作った後に打刻が変わっても、提出時点の打刻で再評価される。照合の判定内容（E-003 の 3 種・E-005）は ONL-005 の AttendanceService#validateBreakCorrection / checkBreakCorrection を参照。
+理由の確認は種別の確認より先（理由が空なら種別・時刻の未入力より先に E-002「理由は必須入力です。」）。</t>
         </is>
       </c>
       <c r="C41" s="9" t="n"/>
@@ -5304,7 +5607,7 @@
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>6.6  RequestStatus#SUBMITTABLE</t>
+          <t>6.6  RequestService#SUBMITTABLE</t>
         </is>
       </c>
       <c r="B68" s="9" t="n"/>
@@ -5321,7 +5624,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>定数（entity/RequestStatus.java に追加）</t>
+          <t>定数（RequestService 内の private 定数。ALL_STATUSES / WITHDRAWABLE と同じ並び）</t>
         </is>
       </c>
       <c r="C69" s="9" t="n"/>
@@ -5337,7 +5640,7 @@
       </c>
       <c r="B70" s="12" t="inlineStr">
         <is>
-          <t>public static final Set&lt;String&gt; SUBMITTABLE = Set.of(DRAFT, RETURNED)</t>
+          <t>private static final Set&lt;String&gt; SUBMITTABLE = Set.of(RequestStatus.DRAFT, RequestStatus.RETURNED)</t>
         </is>
       </c>
       <c r="C70" s="9" t="n"/>
@@ -5457,7 +5760,7 @@
       <c r="E77" s="9" t="n"/>
       <c r="F77" s="10" t="n"/>
     </row>
-    <row r="78" ht="19" customHeight="1">
+    <row r="78" ht="34" customHeight="1">
       <c r="A78" s="11" t="inlineStr">
         <is>
           <t>備考</t>
@@ -5465,7 +5768,7 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>RequestStatus は ONL-005 で定義済み（ALL / WITHDRAWABLE ほか）。定数を 1 つ追記する。</t>
+          <t>RequestStatus クラスには状態の文字列定数と BLOCKING（PENDING, APPROVED）のみがあり、ALL_STATUSES / WITHDRAWABLE / SUBMITTABLE は RequestService の private 定数として実装している。</t>
         </is>
       </c>
       <c r="C78" s="9" t="n"/>
@@ -5685,37 +5988,57 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="8" t="inlineStr">
+    <row r="91" ht="94" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>D-10</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>休憩・離席修正申請の再提出</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="n"/>
+      <c r="D91" s="10" t="n"/>
+      <c r="E91" s="7" t="inlineStr"/>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>承認までに打刻が変わると矛盾した反映になるため。最終承認（ONL-010）でも同じ検証を再実施する。重複判定（E-005）は同じ申請種別・同日の PENDING で、休憩/離席の種別は区別しない</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
         <is>
           <t>6.8  SubmitRequestResponse の定義</t>
         </is>
       </c>
-      <c r="B92" s="9" t="n"/>
-      <c r="C92" s="9" t="n"/>
-      <c r="D92" s="9" t="n"/>
-      <c r="E92" s="9" t="n"/>
-      <c r="F92" s="10" t="n"/>
-    </row>
-    <row r="93" ht="34" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t>処理詳細</t>
-        </is>
-      </c>
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>public record SubmitRequestResponse(Long requestId, String status) { }
-// JSON キーは camelCase（requestId, status）。status は常に "PENDING"</t>
-        </is>
-      </c>
+      <c r="B93" s="9" t="n"/>
       <c r="C93" s="9" t="n"/>
       <c r="D93" s="9" t="n"/>
       <c r="E93" s="9" t="n"/>
       <c r="F93" s="10" t="n"/>
     </row>
+    <row r="94" ht="34" customHeight="1">
+      <c r="A94" s="11" t="inlineStr">
+        <is>
+          <t>処理詳細</t>
+        </is>
+      </c>
+      <c r="B94" s="12" t="inlineStr">
+        <is>
+          <t>public record SubmitRequestResponse(Long requestId, String status) { }
+// JSON キーは camelCase（requestId, status）。status は常に "PENDING"</t>
+        </is>
+      </c>
+      <c r="C94" s="9" t="n"/>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="10" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="85">
+  <mergeCells count="86">
     <mergeCell ref="C61:F61"/>
     <mergeCell ref="B25:F25"/>
     <mergeCell ref="B3:F3"/>
@@ -5734,6 +6057,7 @@
     <mergeCell ref="B37:F37"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B20:F20"/>
+    <mergeCell ref="B94:F94"/>
     <mergeCell ref="C36:F36"/>
     <mergeCell ref="A16:F16"/>
     <mergeCell ref="B72:F72"/>
@@ -5766,8 +6090,9 @@
     <mergeCell ref="B48:F48"/>
     <mergeCell ref="B13:F13"/>
     <mergeCell ref="B73:F73"/>
+    <mergeCell ref="A93:F93"/>
     <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="B91:D91"/>
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="B65:F65"/>
     <mergeCell ref="C21:F21"/>
@@ -5779,7 +6104,6 @@
     <mergeCell ref="A80:F80"/>
     <mergeCell ref="B66:F66"/>
     <mergeCell ref="C7:F7"/>
-    <mergeCell ref="B93:F93"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B14:F14"/>
@@ -5813,7 +6137,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:F103"/>
+  <dimension ref="A2:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5972,7 +6296,7 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>LEAVE / CLOCK_CORRECTION（ck_req_type）</t>
+          <t>LEAVE / CLOCK_CORRECTION / BREAK_CORRECTION（ck_req_type）</t>
         </is>
       </c>
     </row>
@@ -6036,7 +6360,7 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>休暇の開始日／打刻修正の対象日</t>
+          <t>休暇の開始日／打刻修正・休憩離席修正の対象日</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6392,7 @@
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>休暇の終了日／打刻修正は startDate と同値</t>
+          <t>休暇の終了日／打刻修正・休憩離席修正は startDate と同値</t>
         </is>
       </c>
     </row>
@@ -6200,15 +6524,15 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="34" customHeight="1">
+    <row r="15" ht="49" customHeight="1">
       <c r="A15" s="7" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>corrected_break_kind</t>
         </is>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>reason</t>
+          <t>correctedBreakKind</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
@@ -6223,730 +6547,730 @@
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>○ 検証（打刻修正は提出時に必須）</t>
+          <t>○ 検証（BREAK_CORRECTION：null 不可）・打刻照合の入力</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>VARCHAR(200)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="49" customHeight="1">
+          <t>BREAK / AWAY（ck_req_break_kind）。BREAK_CORRECTION のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="34" customHeight="1">
       <c r="A16" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>corrected_break_start</t>
         </is>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>correctedBreakStart</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>LocalDateTime</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>○ 検証（DRAFT / RETURNED のみ可）→ 更新（PENDING）</t>
+          <t>○ 検証（null 不可）・打刻照合の入力</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>DRAFT / PENDING / RETURNED / REJECTED / APPROVED / WITHDRAWN（ck_req_status）</t>
+          <t>修正後の区間の開始日時（JST）。BREAK_CORRECTION のみ</t>
         </is>
       </c>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="A17" s="7" t="inlineStr">
         <is>
+          <t>corrected_break_end</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>correctedBreakEnd</t>
+        </is>
+      </c>
+      <c r="C17" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>○ 検証（null 不可）・打刻照合の入力</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>修正後の区間の終了日時（JST）。BREAK_CORRECTION のみ</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="49" customHeight="1">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>reason</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>○ 検証（打刻修正・休憩離席修正は提出時に必須）</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>VARCHAR(200)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="49" customHeight="1">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>○ 検証（DRAFT / RETURNED のみ可）→ 更新（PENDING）</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>DRAFT / PENDING / RETURNED / REJECTED / APPROVED / WITHDRAWN（ck_req_status）</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="34" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
           <t>current_step</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>currentStep</t>
         </is>
       </c>
-      <c r="C17" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="D17" s="7" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>○ 更新（1。上長なしは 2）</t>
         </is>
       </c>
-      <c r="F17" s="7" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>現在の承認段。DRAFT は 0、提出後は 1 または 2</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="34" customHeight="1">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="21" ht="34" customHeight="1">
+      <c r="A21" s="7" t="inlineStr">
         <is>
           <t>submitted_at</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>submittedAt</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>○ 更新（現在日時。再提出時は上書き）</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>提出日時（JST）。DRAFT は NULL</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="34" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+    <row r="22" ht="34" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D19" s="7" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="7" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="64" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="23" ht="64" customHeight="1">
+      <c r="A23" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C20" s="7" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D20" s="7" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F20" s="7" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_requests_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
+    <row r="24" ht="19" customHeight="1">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t>■ approval_steps</t>
         </is>
       </c>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="10" t="n"/>
-    </row>
-    <row r="22" ht="19" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="10" t="n"/>
+    </row>
+    <row r="25" ht="19" customHeight="1">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D25" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="49" customHeight="1">
-      <c r="A23" s="7" t="inlineStr">
+    <row r="26" ht="49" customHeight="1">
+      <c r="A26" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>— 削除対象（旧ステップ）／新規ステップは採番</t>
         </is>
       </c>
-      <c r="F23" s="7" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>IDENTITY 自動採番</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="49" customHeight="1">
-      <c r="A24" s="7" t="inlineStr">
+    <row r="27" ht="49" customHeight="1">
+      <c r="A27" s="7" t="inlineStr">
         <is>
           <t>request_id</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>requestId</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>○ 削除条件（旧ステップ）／登録（新ステップ）</t>
         </is>
       </c>
-      <c r="F24" s="7" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>FK requests。UNIQUE(request_id, step_no)</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="19" customHeight="1">
-      <c r="A25" s="7" t="inlineStr">
+    <row r="28" ht="19" customHeight="1">
+      <c r="A28" s="7" t="inlineStr">
         <is>
           <t>step_no</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>stepNo</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="D25" s="7" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E25" s="7" t="inlineStr">
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>○ 登録（1 / 2）</t>
         </is>
       </c>
-      <c r="F25" s="7" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>1:上長 / 2:管理者（ck_as_step）</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="34" customHeight="1">
-      <c r="A26" s="7" t="inlineStr">
+    <row r="29" ht="34" customHeight="1">
+      <c r="A29" s="7" t="inlineStr">
         <is>
           <t>approver_id</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>approverId</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D26" s="7" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E26" s="7" t="inlineStr">
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>○ 登録（1段目は上長ID、2段目は NULL）</t>
         </is>
       </c>
-      <c r="F26" s="7" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>FK users。1段目は作成時に上長を設定、2段目は処理時に設定（作成時は NULL）</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="34" customHeight="1">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E27" s="7" t="inlineStr">
-        <is>
-          <t>○ 登録（WAITING）</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>WAITING / APPROVED / RETURNED / REJECTED（ck_as_status）</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="49" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>comment</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>登録しない（NULL）。旧ステップのコメントは削除で失われる</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>VARCHAR(500)。承認者のコメント</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="49" customHeight="1">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>acted_at</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>actedAt</t>
-        </is>
-      </c>
-      <c r="C29" s="7" t="inlineStr">
-        <is>
-          <t>LocalDateTime</t>
-        </is>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="E29" s="7" t="inlineStr">
-        <is>
-          <t>登録しない（NULL）。旧ステップの処理日時も削除で失われる</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>処理日時（JST）</t>
         </is>
       </c>
     </row>
     <row r="30" ht="34" customHeight="1">
       <c r="A30" s="7" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>○ 登録（WAITING）</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>WAITING / APPROVED / RETURNED / REJECTED（ck_as_status）</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="49" customHeight="1">
+      <c r="A31" s="7" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>登録しない（NULL）。旧ステップのコメントは削除で失われる</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>VARCHAR(500)。承認者のコメント</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="49" customHeight="1">
+      <c r="A32" s="7" t="inlineStr">
+        <is>
+          <t>acted_at</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>actedAt</t>
+        </is>
+      </c>
+      <c r="C32" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>登録しない（NULL）。旧ステップの処理日時も削除で失われる</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>処理日時（JST）</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="34" customHeight="1">
+      <c r="A33" s="7" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C30" s="7" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D30" s="7" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E30" s="7" t="inlineStr">
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="7" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="64" customHeight="1">
-      <c r="A31" s="7" t="inlineStr">
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C31" s="7" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E31" s="7" t="inlineStr">
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F31" s="7" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_approval_steps_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="19" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+    <row r="35" ht="19" customHeight="1">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>■ users</t>
         </is>
       </c>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="9" t="n"/>
-      <c r="F32" s="10" t="n"/>
-    </row>
-    <row r="33" ht="19" customHeight="1">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="B35" s="9" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="10" t="n"/>
+    </row>
+    <row r="36" ht="19" customHeight="1">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="34" customHeight="1">
-      <c r="A34" s="7" t="inlineStr">
+    <row r="37" ht="34" customHeight="1">
+      <c r="A37" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C34" s="7" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D34" s="7" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E34" s="7" t="inlineStr">
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>○ 行ロック条件／上長取得</t>
         </is>
       </c>
-      <c r="F34" s="7" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>IDENTITY 自動採番（FOR UPDATE で行ロック）</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="19" customHeight="1">
-      <c r="A35" s="7" t="inlineStr">
+    <row r="38" ht="19" customHeight="1">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>email</t>
         </is>
       </c>
-      <c r="C35" s="7" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D35" s="7" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E35" s="7" t="inlineStr">
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F35" s="7" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>UNIQUE（uq_users_1）、VARCHAR(255)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="19" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>password_hash</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>passwordHash</t>
-        </is>
-      </c>
-      <c r="C36" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D36" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="7" t="inlineStr">
-        <is>
-          <t>BCrypt ハッシュ。VARCHAR(255)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="19" customHeight="1">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C37" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D37" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>○ 通知文面</t>
-        </is>
-      </c>
-      <c r="F37" s="7" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="34" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C38" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D38" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E38" s="7" t="inlineStr">
-        <is>
-          <t>○ 管理者の検索条件（上長なし時）</t>
-        </is>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>EMPLOYEE / MANAGER / ADMIN</t>
         </is>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
       <c r="A39" s="7" t="inlineStr">
         <is>
-          <t>department_id</t>
+          <t>password_hash</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>departmentId</t>
+          <t>passwordHash</t>
         </is>
       </c>
       <c r="C39" s="7" t="inlineStr">
         <is>
-          <t>Long</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
@@ -6956,320 +7280,320 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>FK departments</t>
+          <t>BCrypt ハッシュ。VARCHAR(255)</t>
         </is>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>○ 通知文面</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>VARCHAR(100)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="34" customHeight="1">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>○ 管理者の検索条件（上長なし時）</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>EMPLOYEE / MANAGER / ADMIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="19" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>department_id</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>departmentId</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>FK departments</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="19" customHeight="1">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
           <t>manager_id</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>managerId</t>
         </is>
       </c>
-      <c r="C40" s="7" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D40" s="7" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>可</t>
         </is>
       </c>
-      <c r="E40" s="7" t="inlineStr">
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>○ 1段目承認者の決定</t>
         </is>
       </c>
-      <c r="F40" s="7" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>FK users（自己参照）。1段目承認者の決定に使用</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="19" customHeight="1">
-      <c r="A41" s="7" t="inlineStr">
+    <row r="44" ht="19" customHeight="1">
+      <c r="A44" s="7" t="inlineStr">
         <is>
           <t>hire_date</t>
         </is>
       </c>
-      <c r="B41" s="7" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>hireDate</t>
         </is>
       </c>
-      <c r="C41" s="7" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>LocalDate</t>
         </is>
       </c>
-      <c r="D41" s="7" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E41" s="7" t="inlineStr">
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F41" s="7" t="inlineStr"/>
-    </row>
-    <row r="42" ht="34" customHeight="1">
-      <c r="A42" s="7" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45" ht="34" customHeight="1">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>status</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D42" s="7" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E42" s="7" t="inlineStr">
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>○ ACTIVE 確認／上長の有効確認</t>
         </is>
       </c>
-      <c r="F42" s="7" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>ACTIVE / INACTIVE（既定 ACTIVE）</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="34" customHeight="1">
-      <c r="A43" s="7" t="inlineStr">
+    <row r="46" ht="34" customHeight="1">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F43" s="7" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="64" customHeight="1">
-      <c r="A44" s="7" t="inlineStr">
+    <row r="47" ht="64" customHeight="1">
+      <c r="A47" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B44" s="7" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C44" s="7" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D44" s="7" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E44" s="7" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_users_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="19" customHeight="1">
-      <c r="A45" s="11" t="inlineStr">
+    <row r="48" ht="19" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
         <is>
           <t>■ leave_types</t>
         </is>
       </c>
-      <c r="B45" s="9" t="n"/>
-      <c r="C45" s="9" t="n"/>
-      <c r="D45" s="9" t="n"/>
-      <c r="E45" s="9" t="n"/>
-      <c r="F45" s="10" t="n"/>
-    </row>
-    <row r="46" ht="19" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="B48" s="9" t="n"/>
+      <c r="C48" s="9" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="10" t="n"/>
+    </row>
+    <row r="49" ht="19" customHeight="1">
+      <c r="A49" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D49" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="19" customHeight="1">
-      <c r="A47" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C47" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D47" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>○ 検索条件</t>
-        </is>
-      </c>
-      <c r="F47" s="7" t="inlineStr">
-        <is>
-          <t>IDENTITY 自動採番</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="19" customHeight="1">
-      <c r="A48" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C48" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D48" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>○ 通知文面</t>
-        </is>
-      </c>
-      <c r="F48" s="7" t="inlineStr">
-        <is>
-          <t>UNIQUE（uq_leave_types_1）、VARCHAR(100)</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="19" customHeight="1">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>legal_basis</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>legalBasis</t>
-        </is>
-      </c>
-      <c r="C49" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="E49" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>VARCHAR(100)</t>
         </is>
       </c>
     </row>
     <row r="50" ht="19" customHeight="1">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>is_paid</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>isPaid</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
@@ -7279,20 +7603,24 @@
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F50" s="7" t="inlineStr"/>
-    </row>
-    <row r="51" ht="34" customHeight="1">
+          <t>○ 検索条件</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>IDENTITY 自動採番</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="19" customHeight="1">
       <c r="A51" s="7" t="inlineStr">
         <is>
-          <t>max_days_rule</t>
+          <t>name</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>maxDaysRule</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
@@ -7302,61 +7630,61 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>○ 残日数チェック要否</t>
+          <t>○ 通知文面</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>LIMITED（残日数の範囲内でのみ取得可）／ UNLIMITED（ck_lt_rule）</t>
+          <t>UNIQUE（uq_leave_types_1）、VARCHAR(100)</t>
         </is>
       </c>
     </row>
     <row r="52" ht="19" customHeight="1">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>allow_half_day</t>
+          <t>legal_basis</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>allowHalfDay</t>
+          <t>legalBasis</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>○ 半日指定の可否</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>false の種別は FULL のみ指定可</t>
+          <t>VARCHAR(100)</t>
         </is>
       </c>
     </row>
     <row r="53" ht="19" customHeight="1">
       <c r="A53" s="7" t="inlineStr">
         <is>
-          <t>is_active</t>
+          <t>is_paid</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>isActive</t>
+          <t>isPaid</t>
         </is>
       </c>
       <c r="C53" s="7" t="inlineStr">
@@ -7371,233 +7699,229 @@
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>○ 有効確認</t>
-        </is>
-      </c>
-      <c r="F53" s="7" t="inlineStr">
-        <is>
-          <t>既定 TRUE。false の種別は申請不可</t>
-        </is>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr"/>
     </row>
     <row r="54" ht="34" customHeight="1">
       <c r="A54" s="7" t="inlineStr">
         <is>
+          <t>max_days_rule</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>maxDaysRule</t>
+        </is>
+      </c>
+      <c r="C54" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>○ 残日数チェック要否</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>LIMITED（残日数の範囲内でのみ取得可）／ UNLIMITED（ck_lt_rule）</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="19" customHeight="1">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>allow_half_day</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>allowHalfDay</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>○ 半日指定の可否</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>false の種別は FULL のみ指定可</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="19" customHeight="1">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>is_active</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>isActive</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>○ 有効確認</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>既定 TRUE。false の種別は申請不可</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" s="7" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B54" s="7" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C54" s="7" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F54" s="7" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="64" customHeight="1">
-      <c r="A55" s="7" t="inlineStr">
+    <row r="58" ht="64" customHeight="1">
+      <c r="A58" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B55" s="7" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C55" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E55" s="7" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F55" s="7" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_leave_types_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="19" customHeight="1">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="59" ht="19" customHeight="1">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>■ leave_balances</t>
         </is>
       </c>
-      <c r="B56" s="9" t="n"/>
-      <c r="C56" s="9" t="n"/>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="9" t="n"/>
-      <c r="F56" s="10" t="n"/>
-    </row>
-    <row r="57" ht="19" customHeight="1">
-      <c r="A57" s="6" t="inlineStr">
+      <c r="B59" s="9" t="n"/>
+      <c r="C59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="10" t="n"/>
+    </row>
+    <row r="60" ht="19" customHeight="1">
+      <c r="A60" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D60" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="19" customHeight="1">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C58" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>IDENTITY 自動採番</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="19" customHeight="1">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="inlineStr">
-        <is>
-          <t>userId</t>
-        </is>
-      </c>
-      <c r="C59" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>○ 集計条件</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>FK users</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="19" customHeight="1">
-      <c r="A60" s="7" t="inlineStr">
-        <is>
-          <t>leave_type_id</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="inlineStr">
-        <is>
-          <t>leaveTypeId</t>
-        </is>
-      </c>
-      <c r="C60" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>○ 集計条件</t>
-        </is>
-      </c>
-      <c r="F60" s="7" t="inlineStr">
-        <is>
-          <t>FK leave_types</t>
         </is>
       </c>
     </row>
     <row r="61" ht="19" customHeight="1">
       <c r="A61" s="7" t="inlineStr">
         <is>
-          <t>granted_days</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>grantedDays</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C61" s="7" t="inlineStr">
         <is>
-          <t>BigDecimal</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D61" s="7" t="inlineStr">
@@ -7607,29 +7931,29 @@
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>○ 残日数の集計</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>DECIMAL(4,1)。付与日数</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="34" customHeight="1">
+          <t>IDENTITY 自動採番</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="19" customHeight="1">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>used_days</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>usedDays</t>
+          <t>userId</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>BigDecimal</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
@@ -7639,29 +7963,29 @@
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>○ 残日数の集計</t>
+          <t>○ 集計条件</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>DECIMAL(4,1)。既定 0。消化は ONL-010（承認）で加算</t>
+          <t>FK users</t>
         </is>
       </c>
     </row>
     <row r="63" ht="19" customHeight="1">
       <c r="A63" s="7" t="inlineStr">
         <is>
-          <t>granted_on</t>
+          <t>leave_type_id</t>
         </is>
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>grantedOn</t>
+          <t>leaveTypeId</t>
         </is>
       </c>
       <c r="C63" s="7" t="inlineStr">
         <is>
-          <t>LocalDate</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D63" s="7" t="inlineStr">
@@ -7671,25 +7995,29 @@
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F63" s="7" t="inlineStr"/>
-    </row>
-    <row r="64" ht="34" customHeight="1">
+          <t>○ 集計条件</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>FK leave_types</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="19" customHeight="1">
       <c r="A64" s="7" t="inlineStr">
         <is>
-          <t>expires_on</t>
+          <t>granted_days</t>
         </is>
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>expiresOn</t>
+          <t>grantedDays</t>
         </is>
       </c>
       <c r="C64" s="7" t="inlineStr">
         <is>
-          <t>LocalDate</t>
+          <t>BigDecimal</t>
         </is>
       </c>
       <c r="D64" s="7" t="inlineStr">
@@ -7699,432 +8027,428 @@
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>○ 失効判定（≧ 本日）</t>
+          <t>○ 残日数の集計</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
         <is>
-          <t>失効日（付与日＋2年）。この日までは使用可</t>
+          <t>DECIMAL(4,1)。付与日数</t>
         </is>
       </c>
     </row>
     <row r="65" ht="34" customHeight="1">
       <c r="A65" s="7" t="inlineStr">
         <is>
+          <t>used_days</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>usedDays</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>BigDecimal</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>○ 残日数の集計</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>DECIMAL(4,1)。既定 0。消化は ONL-010（承認）で加算</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="19" customHeight="1">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>granted_on</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>grantedOn</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>LocalDate</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67" ht="34" customHeight="1">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>expires_on</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>expiresOn</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>LocalDate</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>○ 失効判定（≧ 本日）</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>失効日（付与日＋2年）。この日までは使用可</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="34" customHeight="1">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B65" s="7" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C65" s="7" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D65" s="7" t="inlineStr">
+      <c r="D68" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E65" s="7" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F65" s="7" t="inlineStr">
+      <c r="F68" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="64" customHeight="1">
-      <c r="A66" s="7" t="inlineStr">
+    <row r="69" ht="64" customHeight="1">
+      <c r="A69" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B66" s="7" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C66" s="7" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
+      <c r="D69" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E66" s="7" t="inlineStr">
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F66" s="7" t="inlineStr">
+      <c r="F69" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_leave_balances_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="19" customHeight="1">
-      <c r="A67" s="11" t="inlineStr">
+    <row r="70" ht="19" customHeight="1">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>■ holidays</t>
         </is>
       </c>
-      <c r="B67" s="9" t="n"/>
-      <c r="C67" s="9" t="n"/>
-      <c r="D67" s="9" t="n"/>
-      <c r="E67" s="9" t="n"/>
-      <c r="F67" s="10" t="n"/>
-    </row>
-    <row r="68" ht="19" customHeight="1">
-      <c r="A68" s="6" t="inlineStr">
+      <c r="B70" s="9" t="n"/>
+      <c r="C70" s="9" t="n"/>
+      <c r="D70" s="9" t="n"/>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="10" t="n"/>
+    </row>
+    <row r="71" ht="19" customHeight="1">
+      <c r="A71" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B71" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C71" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D68" s="6" t="inlineStr">
+      <c r="D71" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="E71" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F68" s="6" t="inlineStr">
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="19" customHeight="1">
-      <c r="A69" s="7" t="inlineStr">
+    <row r="72" ht="19" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="B69" s="7" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C69" s="7" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="D69" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E69" s="7" t="inlineStr">
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>IDENTITY 自動採番</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="34" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+    <row r="73" ht="34" customHeight="1">
+      <c r="A73" s="7" t="inlineStr">
         <is>
           <t>holiday_date</t>
         </is>
       </c>
-      <c r="B70" s="7" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>holidayDate</t>
         </is>
       </c>
-      <c r="C70" s="7" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>LocalDate</t>
         </is>
       </c>
-      <c r="D70" s="7" t="inlineStr">
+      <c r="D73" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>○ 営業日数の算出（期間内の祝日取得）</t>
         </is>
       </c>
-      <c r="F70" s="7" t="inlineStr">
+      <c r="F73" s="7" t="inlineStr">
         <is>
           <t>UNIQUE（uq_holidays_1）</t>
         </is>
       </c>
     </row>
-    <row r="71" ht="19" customHeight="1">
-      <c r="A71" s="7" t="inlineStr">
+    <row r="74" ht="19" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="B71" s="7" t="inlineStr">
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>name</t>
         </is>
       </c>
-      <c r="C71" s="7" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>String</t>
         </is>
       </c>
-      <c r="D71" s="7" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
         <is>
           <t>不可</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
+      <c r="F74" s="7" t="inlineStr">
         <is>
           <t>VARCHAR(100)</t>
         </is>
       </c>
     </row>
-    <row r="72" ht="34" customHeight="1">
-      <c r="A72" s="7" t="inlineStr">
+    <row r="75" ht="34" customHeight="1">
+      <c r="A75" s="7" t="inlineStr">
         <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B72" s="7" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C72" s="7" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="64" customHeight="1">
-      <c r="A73" s="7" t="inlineStr">
+    <row r="76" ht="64" customHeight="1">
+      <c r="A76" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B73" s="7" t="inlineStr">
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C73" s="7" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr">
+      <c r="D76" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E73" s="7" t="inlineStr">
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
+      <c r="F76" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_holidays_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="74" ht="19" customHeight="1">
-      <c r="A74" s="11" t="inlineStr">
+    <row r="77" ht="19" customHeight="1">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>■ notifications</t>
         </is>
       </c>
-      <c r="B74" s="9" t="n"/>
-      <c r="C74" s="9" t="n"/>
-      <c r="D74" s="9" t="n"/>
-      <c r="E74" s="9" t="n"/>
-      <c r="F74" s="10" t="n"/>
-    </row>
-    <row r="75" ht="19" customHeight="1">
-      <c r="A75" s="6" t="inlineStr">
+      <c r="B77" s="9" t="n"/>
+      <c r="C77" s="9" t="n"/>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="10" t="n"/>
+    </row>
+    <row r="78" ht="19" customHeight="1">
+      <c r="A78" s="6" t="inlineStr">
         <is>
           <t>DB列</t>
         </is>
       </c>
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>Entityフィールド</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>Java型</t>
         </is>
       </c>
-      <c r="D75" s="6" t="inlineStr">
+      <c r="D78" s="6" t="inlineStr">
         <is>
           <t>NULL</t>
         </is>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>この処理での使用</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <t>備考</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="34" customHeight="1">
-      <c r="A76" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C76" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D76" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>—（INSERT 後に採番）</t>
-        </is>
-      </c>
-      <c r="F76" s="7" t="inlineStr">
-        <is>
-          <t>IDENTITY 自動採番（INSERT は NotificationService#notify が行う）</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="49" customHeight="1">
-      <c r="A77" s="7" t="inlineStr">
-        <is>
-          <t>user_id</t>
-        </is>
-      </c>
-      <c r="B77" s="7" t="inlineStr">
-        <is>
-          <t>userId</t>
-        </is>
-      </c>
-      <c r="C77" s="7" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>不可</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>○ 登録（通知先＝現在の承認者。NotificationService 経由）</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>FK users。通知の宛先</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" ht="34" customHeight="1">
-      <c r="A78" s="7" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="B78" s="7" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr">
-        <is>
-          <t>String</t>
-        </is>
-      </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>可</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>○ 登録（REQUEST_SUBMITTED）</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>VARCHAR(30)。NotificationType の値。NULL は旧データのみ（notify は必ず設定）</t>
         </is>
       </c>
     </row>
     <row r="79" ht="34" customHeight="1">
       <c r="A79" s="7" t="inlineStr">
         <is>
-          <t>request_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>requestId</t>
+          <t>id</t>
         </is>
       </c>
       <c r="C79" s="7" t="inlineStr">
@@ -8134,34 +8458,34 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>可</t>
+          <t>不可</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>○ 登録（登録した申請の ID）</t>
+          <t>—（INSERT 後に採番）</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
         <is>
-          <t>FK requests(id)。申請に紐づかない通知は NULL。画面の遷移先判定に使う</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="19" customHeight="1">
+          <t>IDENTITY 自動採番（INSERT は NotificationService#notify が行う）</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="49" customHeight="1">
       <c r="A80" s="7" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>user_id</t>
         </is>
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>userId</t>
         </is>
       </c>
       <c r="C80" s="7" t="inlineStr">
         <is>
-          <t>String</t>
+          <t>Long</t>
         </is>
       </c>
       <c r="D80" s="7" t="inlineStr">
@@ -8171,251 +8495,354 @@
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>○ 登録（通知文面）</t>
+          <t>○ 登録（通知先＝現在の承認者。NotificationService 経由）</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
         <is>
-          <t>VARCHAR(500)</t>
+          <t>FK users。通知の宛先</t>
         </is>
       </c>
     </row>
     <row r="81" ht="34" customHeight="1">
       <c r="A81" s="7" t="inlineStr">
         <is>
-          <t>is_read</t>
+          <t>type</t>
         </is>
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>type</t>
         </is>
       </c>
       <c r="C81" s="7" t="inlineStr">
         <is>
-          <t>boolean</t>
+          <t>String</t>
         </is>
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>不可</t>
+          <t>可</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>○ 登録（FALSE）</t>
+          <t>○ 登録（REQUEST_SUBMITTED）</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
         <is>
-          <t>BOOLEAN、既定 FALSE。Entity のフィールド名は read（getter isRead() / setter setRead）</t>
+          <t>VARCHAR(30)。NotificationType の値。NULL は旧データのみ（notify は必ず設定）</t>
         </is>
       </c>
     </row>
     <row r="82" ht="34" customHeight="1">
       <c r="A82" s="7" t="inlineStr">
         <is>
+          <t>request_id</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="inlineStr">
+        <is>
+          <t>requestId</t>
+        </is>
+      </c>
+      <c r="C82" s="7" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
+        <is>
+          <t>○ 登録（登録した申請の ID）</t>
+        </is>
+      </c>
+      <c r="F82" s="7" t="inlineStr">
+        <is>
+          <t>FK requests(id)。申請に紐づかない通知は NULL。画面の遷移先判定に使う</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="19" customHeight="1">
+      <c r="A83" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="inlineStr">
+        <is>
+          <t>message</t>
+        </is>
+      </c>
+      <c r="C83" s="7" t="inlineStr">
+        <is>
+          <t>String</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
+        <is>
+          <t>○ 登録（通知文面）</t>
+        </is>
+      </c>
+      <c r="F83" s="7" t="inlineStr">
+        <is>
+          <t>VARCHAR(500)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="34" customHeight="1">
+      <c r="A84" s="7" t="inlineStr">
+        <is>
+          <t>is_read</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="inlineStr">
+        <is>
+          <t>read</t>
+        </is>
+      </c>
+      <c r="C84" s="7" t="inlineStr">
+        <is>
+          <t>boolean</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
+        <is>
+          <t>○ 登録（FALSE）</t>
+        </is>
+      </c>
+      <c r="F84" s="7" t="inlineStr">
+        <is>
+          <t>BOOLEAN、既定 FALSE。Entity のフィールド名は read（getter isRead() / setter setRead）</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="34" customHeight="1">
+      <c r="A85" s="7" t="inlineStr">
+        <is>
           <t>created_at</t>
         </is>
       </c>
-      <c r="B82" s="7" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>createdAt</t>
         </is>
       </c>
-      <c r="C82" s="7" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D82" s="7" t="inlineStr">
+      <c r="D85" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E82" s="7" t="inlineStr">
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F82" s="7" t="inlineStr">
+      <c r="F85" s="7" t="inlineStr">
         <is>
           <t>DB の DEFAULT。insertable=false, updatable=false</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="64" customHeight="1">
-      <c r="A83" s="7" t="inlineStr">
+    <row r="86" ht="64" customHeight="1">
+      <c r="A86" s="7" t="inlineStr">
         <is>
           <t>updated_at</t>
         </is>
       </c>
-      <c r="B83" s="7" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>updatedAt</t>
         </is>
       </c>
-      <c r="C83" s="7" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>LocalDateTime</t>
         </is>
       </c>
-      <c r="D83" s="7" t="inlineStr">
+      <c r="D86" s="7" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E83" s="7" t="inlineStr">
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>— トリガで自動</t>
         </is>
       </c>
-      <c r="F83" s="7" t="inlineStr">
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>DB トリガ trg_notifications_updated_at（BEFORE UPDATE / set_updated_at）で更新時に自動更新。Entity は insertable=false, updatable=false（アプリは設定しない）</t>
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="8" t="inlineStr">
-        <is>
-          <t>7.2 SQL・クエリ</t>
-        </is>
-      </c>
-      <c r="B85" s="9" t="n"/>
-      <c r="C85" s="9" t="n"/>
-      <c r="D85" s="9" t="n"/>
-      <c r="E85" s="9" t="n"/>
-      <c r="F85" s="10" t="n"/>
-    </row>
-    <row r="86" ht="49" customHeight="1">
-      <c r="A86" s="11" t="inlineStr">
-        <is>
-          <t>申請者の行ロック（UserRepository#findByIdForUpdate）</t>
-        </is>
-      </c>
-      <c r="B86" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
-        </is>
-      </c>
-      <c r="C86" s="9" t="n"/>
-      <c r="D86" s="9" t="n"/>
-      <c r="E86" s="9" t="n"/>
-      <c r="F86" s="10" t="n"/>
-    </row>
-    <row r="87" ht="49" customHeight="1">
+    <row r="87" ht="19" customHeight="1">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t>申請の行ロック取得（RequestRepository#findByIdForUpdate）</t>
-        </is>
-      </c>
-      <c r="B87" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM requests WHERE id = ? FOR UPDATE</t>
-        </is>
-      </c>
+          <t>■ attendance_records / attendance_breaks</t>
+        </is>
+      </c>
+      <c r="B87" s="9" t="n"/>
       <c r="C87" s="9" t="n"/>
       <c r="D87" s="9" t="n"/>
       <c r="E87" s="9" t="n"/>
       <c r="F87" s="10" t="n"/>
     </row>
-    <row r="88" ht="49" customHeight="1">
-      <c r="A88" s="11" t="inlineStr">
-        <is>
-          <t>休暇種別の取得（LeaveTypeRepository#findById）</t>
-        </is>
-      </c>
-      <c r="B88" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM leave_types WHERE id = ?   -- LEAVE のみ</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="n"/>
-      <c r="D88" s="9" t="n"/>
-      <c r="E88" s="9" t="n"/>
-      <c r="F88" s="10" t="n"/>
-    </row>
-    <row r="89" ht="64" customHeight="1">
-      <c r="A89" s="11" t="inlineStr">
-        <is>
-          <t>期間内の祝日（HolidayRepository#findByHolidayDateBetweenOrderByHolidayDate）</t>
-        </is>
-      </c>
-      <c r="B89" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM holidays WHERE holiday_date BETWEEN ? AND ?   -- LEAVE のみ（営業日数の再計算）</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="n"/>
-      <c r="D89" s="9" t="n"/>
-      <c r="E89" s="9" t="n"/>
-      <c r="F89" s="10" t="n"/>
-    </row>
-    <row r="90" ht="49" customHeight="1">
-      <c r="A90" s="11" t="inlineStr">
-        <is>
-          <t>残日数合計（LeaveBalanceRepository#sumRemainingDays）</t>
-        </is>
-      </c>
-      <c r="B90" s="12" t="inlineStr">
-        <is>
-          <t>SELECT SUM(granted_days - used_days) FROM leave_balances
- WHERE user_id = ? AND leave_type_id = ? AND expires_on &gt;= ?   -- LEAVE かつ上限付き種別のみ</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="n"/>
-      <c r="D90" s="9" t="n"/>
-      <c r="E90" s="9" t="n"/>
-      <c r="F90" s="10" t="n"/>
-    </row>
-    <row r="91" ht="49" customHeight="1">
-      <c r="A91" s="11" t="inlineStr">
-        <is>
-          <t>承認待ち引当日数（RequestRepository#sumPendingLeaveDays）</t>
-        </is>
-      </c>
-      <c r="B91" s="12" t="inlineStr">
-        <is>
-          <t>SELECT SUM(days) FROM requests
- WHERE user_id = ? AND request_type = 'LEAVE' AND leave_type_id = ? AND status = 'PENDING'</t>
-        </is>
-      </c>
-      <c r="C91" s="9" t="n"/>
-      <c r="D91" s="9" t="n"/>
-      <c r="E91" s="9" t="n"/>
-      <c r="F91" s="10" t="n"/>
-    </row>
-    <row r="92" ht="49" customHeight="1">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t>休暇の期間重複（RequestRepository#findOverlappingLeaves）</t>
-        </is>
-      </c>
-      <c r="B92" s="12" t="inlineStr">
-        <is>
-          <t>SELECT * FROM requests
- WHERE user_id = ? AND request_type = 'LEAVE' AND status IN ('PENDING','APPROVED')
-   AND start_date &lt;= ? AND end_date &gt;= ?   -- 自分自身は DRAFT / RETURNED のため含まれない</t>
-        </is>
-      </c>
-      <c r="C92" s="9" t="n"/>
-      <c r="D92" s="9" t="n"/>
-      <c r="E92" s="9" t="n"/>
-      <c r="F92" s="10" t="n"/>
-    </row>
-    <row r="93" ht="34" customHeight="1">
-      <c r="A93" s="11" t="inlineStr">
-        <is>
-          <t>打刻修正の同日重複（existsBy…）</t>
-        </is>
-      </c>
-      <c r="B93" s="12" t="inlineStr">
-        <is>
-          <t>SELECT id FROM requests
- WHERE user_id = ? AND request_type = 'CLOCK_CORRECTION' AND start_date = ? AND status = 'PENDING' LIMIT 1</t>
-        </is>
-      </c>
+    <row r="88" ht="19" customHeight="1">
+      <c r="A88" s="6" t="inlineStr">
+        <is>
+          <t>DB列</t>
+        </is>
+      </c>
+      <c r="B88" s="6" t="inlineStr">
+        <is>
+          <t>Entityフィールド</t>
+        </is>
+      </c>
+      <c r="C88" s="6" t="inlineStr">
+        <is>
+          <t>Java型</t>
+        </is>
+      </c>
+      <c r="D88" s="6" t="inlineStr">
+        <is>
+          <t>NULL</t>
+        </is>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
+        <is>
+          <t>この処理での使用</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>備考</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="49" customHeight="1">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>attendance_records.user_id / work_date</t>
+        </is>
+      </c>
+      <c r="B89" s="7" t="inlineStr">
+        <is>
+          <t>userId / workDate</t>
+        </is>
+      </c>
+      <c r="C89" s="7" t="inlineStr">
+        <is>
+          <t>Long / LocalDate</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>不可</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>○ 検索条件（対象日 1 日。BREAK_CORRECTION のみ）</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>(user_id, work_date) UNIQUE</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="34" customHeight="1">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>attendance_records.clock_in / clock_out</t>
+        </is>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>clockIn / clockOut</t>
+        </is>
+      </c>
+      <c r="C90" s="7" t="inlineStr">
+        <is>
+          <t>LocalDateTime</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>可</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>○ 範囲チェック（出勤〜退勤）</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>clock_out が NULL（未退勤）なら「出勤以降」</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="64" customHeight="1">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>attendance_breaks.attendance_record_id / kind / start_at / end_at</t>
+        </is>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>attendanceRecordId / kind / startAt / endAt</t>
+        </is>
+      </c>
+      <c r="C91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>○ 重なり判定の入力（参照のみ）</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>詳細は ONL-024 の 7.1／ONL-005 の validateBreakCorrection</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="8" t="inlineStr">
+        <is>
+          <t>7.2 SQL・クエリ</t>
+        </is>
+      </c>
+      <c r="B93" s="9" t="n"/>
       <c r="C93" s="9" t="n"/>
       <c r="D93" s="9" t="n"/>
       <c r="E93" s="9" t="n"/>
@@ -8424,13 +8851,12 @@
     <row r="94" ht="49" customHeight="1">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t>申請の更新（Dirty Checking）</t>
+          <t>申請者の行ロック（UserRepository#findByIdForUpdate）</t>
         </is>
       </c>
       <c r="B94" s="12" t="inlineStr">
         <is>
-          <t>UPDATE requests SET status = 'PENDING', current_step = 1, submitted_at = ?, days = ? WHERE id = ?
-  -- 実際は Hibernate の設定により全列を SET する場合がある。updated_at は SET しない（DB トリガ trg_requests_updated_at で自動更新）</t>
+          <t>SELECT * FROM users WHERE id = ? FOR UPDATE</t>
         </is>
       </c>
       <c r="C94" s="9" t="n"/>
@@ -8438,15 +8864,15 @@
       <c r="E94" s="9" t="n"/>
       <c r="F94" s="10" t="n"/>
     </row>
-    <row r="95" ht="64" customHeight="1">
+    <row r="95" ht="49" customHeight="1">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t>旧承認ステップの削除（ApprovalStepRepository#deleteByRequestId）</t>
+          <t>申請の行ロック取得（RequestRepository#findByIdForUpdate）</t>
         </is>
       </c>
       <c r="B95" s="12" t="inlineStr">
         <is>
-          <t>DELETE FROM approval_steps WHERE request_id = ?   -- 先に上記 UPDATE がフラッシュされる</t>
+          <t>SELECT * FROM requests WHERE id = ? FOR UPDATE</t>
         </is>
       </c>
       <c r="C95" s="9" t="n"/>
@@ -8457,13 +8883,12 @@
     <row r="96" ht="49" customHeight="1">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t>上長の取得／管理者一覧（ApprovalRouteService）</t>
+          <t>休暇種別の取得（LeaveTypeRepository#findById）</t>
         </is>
       </c>
       <c r="B96" s="12" t="inlineStr">
         <is>
-          <t>SELECT * FROM users WHERE id = ?   （上長）
-SELECT * FROM users WHERE role = 'ADMIN' AND status = 'ACTIVE'   （上長なし時の通知先）</t>
+          <t>SELECT * FROM leave_types WHERE id = ?   -- LEAVE のみ</t>
         </is>
       </c>
       <c r="C96" s="9" t="n"/>
@@ -8471,16 +8896,15 @@
       <c r="E96" s="9" t="n"/>
       <c r="F96" s="10" t="n"/>
     </row>
-    <row r="97" ht="49" customHeight="1">
+    <row r="97" ht="64" customHeight="1">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t>承認ステップの登録（ApprovalStepRepository#saveAll）</t>
+          <t>期間内の祝日（HolidayRepository#findByHolidayDateBetweenOrderByHolidayDate）</t>
         </is>
       </c>
       <c r="B97" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO approval_steps (request_id, step_no, approver_id, status, comment, acted_at)
-VALUES (?, 1, &lt;上長ID&gt;, 'WAITING', NULL, NULL), (?, 2, NULL, 'WAITING', NULL, NULL)   -- 実際は1行ずつ INSERT</t>
+          <t>SELECT * FROM holidays WHERE holiday_date BETWEEN ? AND ?   -- LEAVE のみ（営業日数の再計算）</t>
         </is>
       </c>
       <c r="C97" s="9" t="n"/>
@@ -8488,15 +8912,16 @@
       <c r="E97" s="9" t="n"/>
       <c r="F97" s="10" t="n"/>
     </row>
-    <row r="98" ht="34" customHeight="1">
+    <row r="98" ht="49" customHeight="1">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t>current_step の更新（上長なしの場合のみ）</t>
+          <t>残日数合計（LeaveBalanceRepository#sumRemainingDays）</t>
         </is>
       </c>
       <c r="B98" s="12" t="inlineStr">
         <is>
-          <t>UPDATE requests SET current_step = 2 WHERE id = ?   -- 同一トランザクションの Dirty Checking（上記 UPDATE と 1 回にまとまる）</t>
+          <t>SELECT SUM(granted_days - used_days) FROM leave_balances
+ WHERE user_id = ? AND leave_type_id = ? AND expires_on &gt;= ?   -- LEAVE かつ上限付き種別のみ</t>
         </is>
       </c>
       <c r="C98" s="9" t="n"/>
@@ -8504,16 +8929,16 @@
       <c r="E98" s="9" t="n"/>
       <c r="F98" s="10" t="n"/>
     </row>
-    <row r="99" ht="34" customHeight="1">
+    <row r="99" ht="49" customHeight="1">
       <c r="A99" s="11" t="inlineStr">
         <is>
-          <t>通知の登録（NotificationService#notify）</t>
+          <t>承認待ち引当日数（RequestRepository#sumPendingLeaveDays）</t>
         </is>
       </c>
       <c r="B99" s="12" t="inlineStr">
         <is>
-          <t>INSERT INTO notifications (user_id, type, request_id, message, is_read)
-  VALUES (?, 'REQUEST_SUBMITTED', ?, ?, FALSE)   -- 承認者の人数分。created_at / updated_at は DB の DEFAULT</t>
+          <t>SELECT SUM(days) FROM requests
+ WHERE user_id = ? AND request_type = 'LEAVE' AND leave_type_id = ? AND status = 'PENDING'</t>
         </is>
       </c>
       <c r="C99" s="9" t="n"/>
@@ -8521,95 +8946,250 @@
       <c r="E99" s="9" t="n"/>
       <c r="F99" s="10" t="n"/>
     </row>
-    <row r="101">
-      <c r="A101" s="8" t="inlineStr">
-        <is>
-          <t>7.3 設定値</t>
-        </is>
-      </c>
-      <c r="B101" s="9" t="n"/>
+    <row r="100" ht="49" customHeight="1">
+      <c r="A100" s="11" t="inlineStr">
+        <is>
+          <t>休暇の期間重複（RequestRepository#findOverlappingLeaves）</t>
+        </is>
+      </c>
+      <c r="B100" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM requests
+ WHERE user_id = ? AND request_type = 'LEAVE' AND status IN ('PENDING','APPROVED')
+   AND start_date &lt;= ? AND end_date &gt;= ?   -- 自分自身は DRAFT / RETURNED のため含まれない</t>
+        </is>
+      </c>
+      <c r="C100" s="9" t="n"/>
+      <c r="D100" s="9" t="n"/>
+      <c r="E100" s="9" t="n"/>
+      <c r="F100" s="10" t="n"/>
+    </row>
+    <row r="101" ht="49" customHeight="1">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>打刻修正・休憩離席修正の同日重複（existsBy…）</t>
+        </is>
+      </c>
+      <c r="B101" s="12" t="inlineStr">
+        <is>
+          <t>SELECT id FROM requests
+ WHERE user_id = ? AND request_type = ?   -- CLOCK_CORRECTION または BREAK_CORRECTION
+   AND start_date = ? AND status = 'PENDING' LIMIT 1</t>
+        </is>
+      </c>
       <c r="C101" s="9" t="n"/>
       <c r="D101" s="9" t="n"/>
       <c r="E101" s="9" t="n"/>
       <c r="F101" s="10" t="n"/>
     </row>
-    <row r="102" ht="19" customHeight="1">
-      <c r="A102" s="6" t="inlineStr">
+    <row r="102" ht="79" customHeight="1">
+      <c r="A102" s="11" t="inlineStr">
+        <is>
+          <t>休憩・離席修正の打刻照合（AttendanceService#validateBreakCorrection。BREAK_CORRECTION のみ）</t>
+        </is>
+      </c>
+      <c r="B102" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM attendance_records WHERE user_id = ? AND work_date BETWEEN ? AND ?   -- 対象日 〜 対象日
+SELECT * FROM attendance_breaks WHERE attendance_record_id = ? ORDER BY start_at</t>
+        </is>
+      </c>
+      <c r="C102" s="9" t="n"/>
+      <c r="D102" s="9" t="n"/>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="10" t="n"/>
+    </row>
+    <row r="103" ht="49" customHeight="1">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>申請の更新（Dirty Checking）</t>
+        </is>
+      </c>
+      <c r="B103" s="12" t="inlineStr">
+        <is>
+          <t>UPDATE requests SET status = 'PENDING', current_step = 1, submitted_at = ?, days = ? WHERE id = ?
+  -- 実際は Hibernate の設定により全列を SET する場合がある。updated_at は SET しない（DB トリガ trg_requests_updated_at で自動更新）</t>
+        </is>
+      </c>
+      <c r="C103" s="9" t="n"/>
+      <c r="D103" s="9" t="n"/>
+      <c r="E103" s="9" t="n"/>
+      <c r="F103" s="10" t="n"/>
+    </row>
+    <row r="104" ht="64" customHeight="1">
+      <c r="A104" s="11" t="inlineStr">
+        <is>
+          <t>旧承認ステップの削除（ApprovalStepRepository#deleteByRequestId）</t>
+        </is>
+      </c>
+      <c r="B104" s="12" t="inlineStr">
+        <is>
+          <t>DELETE FROM approval_steps WHERE request_id = ?   -- 先に上記 UPDATE がフラッシュされる</t>
+        </is>
+      </c>
+      <c r="C104" s="9" t="n"/>
+      <c r="D104" s="9" t="n"/>
+      <c r="E104" s="9" t="n"/>
+      <c r="F104" s="10" t="n"/>
+    </row>
+    <row r="105" ht="49" customHeight="1">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>上長の取得／管理者一覧（ApprovalRouteService）</t>
+        </is>
+      </c>
+      <c r="B105" s="12" t="inlineStr">
+        <is>
+          <t>SELECT * FROM users WHERE id = ?   （上長）
+SELECT * FROM users WHERE role = 'ADMIN' AND status = 'ACTIVE'   （上長なし時の通知先）</t>
+        </is>
+      </c>
+      <c r="C105" s="9" t="n"/>
+      <c r="D105" s="9" t="n"/>
+      <c r="E105" s="9" t="n"/>
+      <c r="F105" s="10" t="n"/>
+    </row>
+    <row r="106" ht="49" customHeight="1">
+      <c r="A106" s="11" t="inlineStr">
+        <is>
+          <t>承認ステップの登録（ApprovalStepRepository#saveAll）</t>
+        </is>
+      </c>
+      <c r="B106" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO approval_steps (request_id, step_no, approver_id, status, comment, acted_at)
+VALUES (?, 1, &lt;上長ID&gt;, 'WAITING', NULL, NULL), (?, 2, NULL, 'WAITING', NULL, NULL)   -- 実際は1行ずつ INSERT</t>
+        </is>
+      </c>
+      <c r="C106" s="9" t="n"/>
+      <c r="D106" s="9" t="n"/>
+      <c r="E106" s="9" t="n"/>
+      <c r="F106" s="10" t="n"/>
+    </row>
+    <row r="107" ht="34" customHeight="1">
+      <c r="A107" s="11" t="inlineStr">
+        <is>
+          <t>current_step の更新（上長なしの場合のみ）</t>
+        </is>
+      </c>
+      <c r="B107" s="12" t="inlineStr">
+        <is>
+          <t>UPDATE requests SET current_step = 2 WHERE id = ?   -- 同一トランザクションの Dirty Checking（上記 UPDATE と 1 回にまとまる）</t>
+        </is>
+      </c>
+      <c r="C107" s="9" t="n"/>
+      <c r="D107" s="9" t="n"/>
+      <c r="E107" s="9" t="n"/>
+      <c r="F107" s="10" t="n"/>
+    </row>
+    <row r="108" ht="34" customHeight="1">
+      <c r="A108" s="11" t="inlineStr">
+        <is>
+          <t>通知の登録（NotificationService#notify）</t>
+        </is>
+      </c>
+      <c r="B108" s="12" t="inlineStr">
+        <is>
+          <t>INSERT INTO notifications (user_id, type, request_id, message, is_read)
+  VALUES (?, 'REQUEST_SUBMITTED', ?, ?, FALSE)   -- 承認者の人数分。created_at / updated_at は DB の DEFAULT</t>
+        </is>
+      </c>
+      <c r="C108" s="9" t="n"/>
+      <c r="D108" s="9" t="n"/>
+      <c r="E108" s="9" t="n"/>
+      <c r="F108" s="10" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="8" t="inlineStr">
+        <is>
+          <t>7.3 設定値</t>
+        </is>
+      </c>
+      <c r="B110" s="9" t="n"/>
+      <c r="C110" s="9" t="n"/>
+      <c r="D110" s="9" t="n"/>
+      <c r="E110" s="9" t="n"/>
+      <c r="F110" s="10" t="n"/>
+    </row>
+    <row r="111" ht="19" customHeight="1">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>キー</t>
         </is>
       </c>
-      <c r="B102" s="6" t="inlineStr">
+      <c r="B111" s="6" t="inlineStr">
         <is>
           <t>格納場所</t>
         </is>
       </c>
-      <c r="C102" s="6" t="inlineStr">
+      <c r="C111" s="6" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D102" s="10" t="n"/>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="D111" s="10" t="n"/>
+      <c r="E111" s="6" t="inlineStr">
         <is>
           <t>備考</t>
         </is>
       </c>
-      <c r="F102" s="10" t="n"/>
-    </row>
-    <row r="103" ht="49" customHeight="1">
-      <c r="A103" s="7" t="inlineStr">
+      <c r="F111" s="10" t="n"/>
+    </row>
+    <row r="112" ht="49" customHeight="1">
+      <c r="A112" s="7" t="inlineStr">
         <is>
           <t>spring.jpa.properties.hibernate.jdbc.time_zone</t>
         </is>
       </c>
-      <c r="B103" s="7" t="inlineStr">
+      <c r="B112" s="7" t="inlineStr">
         <is>
           <t>application.properties</t>
         </is>
       </c>
-      <c r="C103" s="7" t="inlineStr">
+      <c r="C112" s="7" t="inlineStr">
         <is>
           <t>Asia/Tokyo</t>
         </is>
       </c>
-      <c r="D103" s="10" t="n"/>
-      <c r="E103" s="7" t="inlineStr">
+      <c r="D112" s="10" t="n"/>
+      <c r="E112" s="7" t="inlineStr">
         <is>
           <t>ONL-005 と共通</t>
         </is>
       </c>
-      <c r="F103" s="10" t="n"/>
+      <c r="F112" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="28">
-    <mergeCell ref="B91:F91"/>
-    <mergeCell ref="B90:F90"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="B93:F93"/>
+  <mergeCells count="30">
+    <mergeCell ref="B106:F106"/>
+    <mergeCell ref="B100:F100"/>
+    <mergeCell ref="E111:F111"/>
     <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A101:F101"/>
     <mergeCell ref="B96:F96"/>
+    <mergeCell ref="B102:F102"/>
+    <mergeCell ref="B105:F105"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A85:F85"/>
-    <mergeCell ref="B86:F86"/>
-    <mergeCell ref="C103:D103"/>
-    <mergeCell ref="E103:F103"/>
-    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="C112:D112"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B88:F88"/>
-    <mergeCell ref="B87:F87"/>
-    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="B101:F101"/>
+    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="B103:F103"/>
+    <mergeCell ref="B108:F108"/>
     <mergeCell ref="B99:F99"/>
-    <mergeCell ref="B92:F92"/>
+    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A77:F77"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="B95:F95"/>
-    <mergeCell ref="A45:F45"/>
-    <mergeCell ref="B89:F89"/>
+    <mergeCell ref="B104:F104"/>
+    <mergeCell ref="A70:F70"/>
+    <mergeCell ref="A110:F110"/>
+    <mergeCell ref="E112:F112"/>
     <mergeCell ref="B94:F94"/>
-    <mergeCell ref="C102:D102"/>
-    <mergeCell ref="E102:F102"/>
+    <mergeCell ref="C111:D111"/>
+    <mergeCell ref="A87:F87"/>
     <mergeCell ref="B97:F97"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
